--- a/docs/marketready-question-bank.xlsx
+++ b/docs/marketready-question-bank.xlsx
@@ -480,7 +480,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from code on 2026-09-02T19:38:39.475Z. Regenerate with: npm run docs:bank</t>
+          <t>Generated from code on 2026-09-02T21:30:54.262Z. Regenerate with: npm run docs:bank</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>logistics_3pl</t>
+          <t>cre_owner</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>logistics_3pl</t>
+          <t>cre_owner</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>logistics_3pl</t>
+          <t>cre_owner</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>logistics_3pl</t>
+          <t>cre_owner</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>logistics_3pl</t>
+          <t>cre_owner</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -675,12 +675,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>logistics_3pl</t>
+          <t>cre_owner</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>business changes 0; profile recent change true/false</t>
+          <t>business changes 0; profile recent acquisition true/false</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -692,22 +692,22 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>fleet_branch</t>
+          <t>management_agreement_branch</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>logistics_3pl</t>
+          <t>cre_owner</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>hasVehicles true; fleet controls 0</t>
+          <t>usesThirdPartyManager true; management agreement 0</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>branch applicable; critical flag br_fleet_controls</t>
+          <t>branch applicable; critical flag br_management_agreement</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>light_manufacturing</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>module=contracts; COI 0, requirements 1, subcontractor 1</t>
+          <t>module=contracts; COI 0, requirements 1, vendor transfer 1</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Who owns the insurance program, when renewal work begins, and how limits are decided.</t>
+          <t>Who owns the insurance program across the portfolio, when renewal work begins, and how limits and deductibles are decided.</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Data &amp; market readiness</t>
+          <t>Property data &amp; market readiness</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>How well exposure data and business changes are documented and presented to carriers.</t>
+          <t>How well the statement of values, acquisitions and dispositions, and building updates are documented and presented to carriers.</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Cyber, payment authorization, safety, and training practices that underwriters ask about.</t>
+          <t>Tenant and applicant data, rent and vendor payment controls, and property inspection and life-safety practices.</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>How incidents are reported, open claims are reviewed, and root causes are tracked.</t>
+          <t>How incidents at the properties are reported, open claims are reviewed, and corrective actions are tracked.</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Whether contracts, insurance requirements, and certificate verification work as one system.</t>
+          <t>Whether leases, vendor agreements, insurance requirements, and certificate verification work as one system.</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>How new locations, products, technology, and regulations are reviewed for risk impact.</t>
+          <t>How acquisitions, new property types, regulations, and new exposures like EV charging are reviewed for risk impact.</t>
         </is>
       </c>
     </row>
@@ -1006,88 +1006,88 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>logistics_3pl</t>
+          <t>cre_owner</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>3PL, warehousing &amp; distribution</t>
+          <t>Commercial real estate owner / investor</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>3PL / Warehousing</t>
+          <t>Commercial RE</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Third-party logistics, public and contract warehousing, cold chain, fulfillment, and regional distribution.</t>
+          <t>Office, industrial and flex, retail, mixed-use, and net-lease portfolios, whether self-managed or with a third-party manager.</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>493110, 493120, 484110, 484121, 488510</t>
+          <t>531110, 531120, 531190, 531390</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Carriers evaluating warehousing and 3PL accounts look closely at warehouse legal liability, cargo and customer contracts, fleet controls, fire protection, and how consistently incidents are reported.</t>
+          <t>Property underwriters price commercial portfolios on the quality of the statement of values, construction and protection data, roof and building-system updates, how carrier recommendations were handled, and how lease and vendor requirements transfer risk.</t>
         </is>
       </c>
       <c r="H2" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I2" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>1.5</v>
-      </c>
       <c r="M2" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>light_manufacturing</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Light manufacturing</t>
+          <t>Multifamily owner / property manager</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Multifamily</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Fabrication, assembly, food and beverage, plastics, packaging, electronics, and other light industrial operations.</t>
+          <t>Apartment communities, student and workforce housing, and third-party residential management.</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>332, 333, 335, 311, 326, 339</t>
+          <t>531110, 531311, 531390</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Underwriters reviewing manufacturers focus on product liability and recall exposure, machine guarding and workers' compensation history, property valuation, business interruption, and supplier and customer contract terms.</t>
+          <t>Multifamily carriers look closely at habitability and life-safety practices, renters insurance enforcement, fair-housing training, vendor certificates for snow and ice and contractors, claim frequency, and how quickly incidents are reported.</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
@@ -1103,7 +1103,7 @@
         <v>1.25</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="M3" s="4" t="n">
         <v>1</v>
@@ -1117,26 +1117,30 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Other middle-market business</t>
+          <t>Other real estate operator</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other RE</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Any other commercial operation. Uses generic weighting.</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr"/>
+          <t>Self-storage, hospitality assets, senior housing, associations, land, or a mixed portfolio. Uses generic weighting.</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
       <c r="F4" s="4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Carriers evaluate every account on the quality of its exposure data, controls, claims history, and the clarity of the story that accompanies the submission.</t>
+          <t>Carriers evaluate every real estate account on the quality of its property data, the controls at each location, claims history, and the clarity of the story that accompanies the submission.</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
@@ -1224,12 +1228,12 @@
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>weight_logistics_3pl</t>
+          <t>weight_cre_owner</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>weight_light_manufacturing</t>
+          <t>weight_multifamily</t>
         </is>
       </c>
       <c r="J1" s="3" t="inlineStr">
@@ -1270,12 +1274,12 @@
       <c r="E2" s="4" t="inlineStr"/>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>When does renewal preparation typically begin relative to your policy expiration?</t>
+          <t>When does renewal preparation for the portfolio typically begin relative to policy expiration?</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Carriers reward complete submissions delivered early. Late starts compress negotiation time.</t>
+          <t>Property markets reward complete, early submissions. A late start means values and building updates never make it into the story carriers see.</t>
         </is>
       </c>
       <c r="H2" s="4" t="n">
@@ -1292,7 +1296,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>Renewal preparation appears to begin inside 30 days of expiration, which limits the ability to document controls and approach alternative markets.</t>
+          <t>Renewal preparation appears to begin inside 30 days of expiration, which limits the ability to update values, document building improvements, and approach alternative markets.</t>
         </is>
       </c>
     </row>
@@ -1318,10 +1322,14 @@
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Who owns the insurance program internally, and how is that responsibility defined?</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr"/>
+          <t>Who owns the insurance program for the portfolio, and how is that responsibility defined?</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>In many real estate organizations this sits between ownership, an asset manager, a controller, and the property manager.</t>
+        </is>
+      </c>
       <c r="H3" s="4" t="n">
         <v>2</v>
       </c>
@@ -1350,18 +1358,18 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Limit rationale</t>
+          <t>Limit and deductible rationale</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>How are policy limits and deductibles decided each year?</t>
+          <t>How are liability limits, property deductibles, and umbrella limits decided each year?</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>This question asks about your decision process, not whether the limits are adequate.</t>
+          <t>This asks about your decision process, not whether the limits are adequate.</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
@@ -1392,16 +1400,20 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Exposure data</t>
+          <t>Statement of values</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>How are exposure values (payroll, revenue, property values, vehicle schedules, inventory) validated before submission?</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
+          <t>How is the statement of values (replacement cost, construction and protection details, occupancy, square footage, year built, updates) maintained and validated before submission?</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Replacement cost that is dictated by the insurer, or carried forward, is the most common reason a property submission is discounted.</t>
+        </is>
+      </c>
       <c r="H5" s="4" t="n">
         <v>3</v>
       </c>
@@ -1430,13 +1442,13 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Business change documentation</t>
+          <t>Portfolio changes</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>How are operational changes (new services, locations, equipment, customers, headcount) communicated to your insurance program during the year?</t>
+          <t>How are acquisitions, dispositions, renovations, new leases, and occupancy changes communicated to your insurance program during the year?</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
@@ -1468,18 +1480,18 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Submission visibility</t>
+          <t>Your risk profile in the market</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>How much visibility do you have into what is actually sent to carriers about your company?</t>
+          <t>Do you know how your story is being told in the marketplace, and do you see what is sent to insurance companies about the portfolio?</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>The underwriting story is the narrative and evidence that accompanies applications and loss runs.</t>
+          <t>Brokers who never saw your environmental consultant's report, your capital plan, or your maintenance program cannot present them.</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
@@ -1510,21 +1522,25 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Cyber controls</t>
+          <t>Data security</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Which of the following best describes your cyber controls (MFA, backups, endpoint protection, incident response)?</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
+          <t>What data do you hold on tenants, applicants, and investors, how is it stored and shared, and how is it protected?</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Applications, background checks, banking details, and investor reporting are all sensitive. Property-management software vendors should be part of the answer.</t>
+        </is>
+      </c>
       <c r="H8" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>2</v>
@@ -1534,7 +1550,7 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>Multi-factor authentication and tested backups do not appear to be consistently in place. Most cyber carriers now treat these as minimum requirements.</t>
+          <t>Tenant, applicant, or investor data appears to be held without a data security program. Cyber carriers treat MFA and encryption as minimum requirements.</t>
         </is>
       </c>
     </row>
@@ -1554,13 +1570,13 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Payment &amp; wire controls</t>
+          <t>Funds transfer security</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>How are changes to vendor bank details and outgoing wire requests verified?</t>
+          <t>How is the flow of funds controlled: rent collection, security deposits, vendor payments, wires, and changes to vendor bank details?</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
@@ -1578,7 +1594,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Vendor bank-detail changes and wires may be released on an email or phone request alone, which is the most common path for social-engineering losses.</t>
+          <t>Wires and vendor bank-detail changes may be released on an email or phone request alone, which is the most common path for social-engineering losses in property operations.</t>
         </is>
       </c>
     </row>
@@ -1598,16 +1614,20 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Safety &amp; training</t>
+          <t>Inspections, life safety &amp; maintenance</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>How are safety programs, training, and inspections documented?</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr"/>
+          <t>How are property inspections, life-safety systems, lighting, and preventive maintenance documented across the portfolio?</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Documented inspections and maintenance logs are what carriers credit; practices that exist only in the property manager's head do not count.</t>
+        </is>
+      </c>
       <c r="H10" s="4" t="n">
         <v>3</v>
       </c>
@@ -1636,13 +1656,13 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Incident reporting</t>
+          <t>Claim intake &amp; reporting</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>What happens when an incident or potential claim occurs?</t>
+          <t>What policies and procedures make sure incidents at the properties (injuries, fires, water losses, tenant claims) are reported and managed properly?</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -1660,7 +1680,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>Incidents appear to be reported inconsistently or late. Late reporting is a frequent driver of higher claim costs and coverage disputes.</t>
+          <t>Incidents appear to be reported inconsistently or late. Late reporting is a frequent driver of higher claim costs and coverage disputes, especially on liability claims.</t>
         </is>
       </c>
     </row>
@@ -1680,16 +1700,20 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Open claim review</t>
+          <t>Claims management &amp; advocacy</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>How often are open claims and reserves reviewed with your broker or carrier?</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr"/>
+          <t>How are open claims, reserves, carrier-assigned counsel, and public adjusters managed?</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>The workshop asks whether your broker has a systematic process: frequency of updates, claims positioning, policy review, legal guidance, and advocacy.</t>
+        </is>
+      </c>
       <c r="H12" s="4" t="n">
         <v>2</v>
       </c>
@@ -1724,7 +1748,7 @@
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>After an incident, how are root causes identified and corrective actions tracked?</t>
+          <t>After an incident at a property, how are root causes identified and corrective actions tracked?</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
@@ -1756,21 +1780,21 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Signed contracts</t>
+          <t>Vendor &amp; contractor contracts</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Before work begins with customers, vendors, or subcontractors, how consistently are written contracts in place?</t>
+          <t>Tell us about the contracts you use with vendors and contractors at the properties (snow and ice, landscaping, security, renovations). Are master agreements in place with key vendors?</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>2</v>
@@ -1794,13 +1818,13 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Insurance requirements</t>
+          <t>Insurance requirements in leases &amp; contracts</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>How do you determine what insurance to require from the parties you work with, and what they require from you?</t>
+          <t>How are insurance requirements set for tenants in leases and for vendors in contracts, and how are lender and management-agreement requirements on you tracked?</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
@@ -1832,13 +1856,13 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Certificate verification</t>
+          <t>Certificate tracking</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>How are certificates of insurance and endorsements (additional insured, waiver of subrogation) verified?</t>
+          <t>What is your process for vetting vendors and contractors who work at the properties, and how are certificates of insurance and endorsements tracked?</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
@@ -1846,7 +1870,7 @@
         <v>3</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>2</v>
@@ -1856,7 +1880,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>Certificates of insurance are collected but not reviewed, so contractual risk transfer may not be operating when a loss occurs.</t>
+          <t>Vendor certificates of insurance are collected but not reviewed, so the indemnity and additional-insured protection in your contracts may not be operating when a loss occurs.</t>
         </is>
       </c>
     </row>
@@ -1876,18 +1900,18 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Annual risk review</t>
+          <t>Frequent risk assessment</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Does leadership conduct a structured risk review outside of the insurance renewal?</t>
+          <t>How often is a thorough risk assessment of the portfolio performed outside of an insurance policy renewal?</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>A risk review looks at operations, contracts, and controls, not just the policies being renewed.</t>
+          <t>A risk review looks at operations, contracts, properties, and controls, not just the policies being renewed.</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
@@ -1918,13 +1942,13 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Regulatory monitoring</t>
+          <t>Regulatory &amp; compliance monitoring</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>How are regulatory and compliance changes affecting your operations monitored?</t>
+          <t>How are regulatory and compliance changes affecting the properties monitored (fair housing, ADA, local habitability and safety ordinances, energy and benchmarking rules)?</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
@@ -1956,16 +1980,20 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>New activity review</t>
+          <t>New exposure review</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>When you add a new location, product, service, technology, or major customer, is risk and insurance impact reviewed beforehand?</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr"/>
+          <t>When you acquire a property, add a new property type, allow short-term rentals, or add EV charging or lithium-battery storage, is the risk and insurance impact reviewed beforehand?</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>The workshop found owners who had never heard of the lithium-battery exposure and were about to add car chargers.</t>
+        </is>
+      </c>
       <c r="H19" s="4" t="n">
         <v>2</v>
       </c>
@@ -1994,7 +2022,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Property valuation &amp; building updates</t>
+          <t>Carrier recommendations &amp; building updates</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -2004,12 +2032,12 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>For the buildings you own, how are replacement values, business-interruption values, flood exposure, building updates (roof, sprinklers, electrical), and carrier loss-control recommendations documented and tracked?</t>
+          <t>What is your procedure for dealing with insurance company recommendations (sprinklers, wiring, boilers, roofs), and how are building updates and flood exposure documented?</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Carriers issue recommendations after inspections. How you respond to them is part of the underwriting story.</t>
+          <t>Carriers issue recommendations after inspections. Owners who track and close them, and show the carrier, negotiate from strength.</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
@@ -2030,27 +2058,27 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>br_fleet_controls</t>
+          <t>br_management_agreement</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>operational_controls</t>
+          <t>contractual_risk_transfer</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Fleet &amp; driver controls</t>
+          <t>Management agreements</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>hasVehicles</t>
+          <t>usesThirdPartyManager</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>How are drivers screened and vehicles managed (MVRs, telematics, hired and non-owned auto)?</t>
+          <t>How do your management agreements address insurance and indemnification obligations between you and the third-party property manager?</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr"/>
@@ -2058,7 +2086,7 @@
         <v>3</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>2</v>
@@ -2068,7 +2096,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>Motor vehicle records do not appear to be run consistently, which commercial auto underwriters treat as a primary control.</t>
+          <t>Insurance and indemnification terms in the property-management agreement have not been reviewed, so it is unclear who is covered for a loss at a managed property.</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2106,17 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>br_subcontractor_transfer</t>
+          <t>br_vendor_transfer</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>contractual_risk_transfer</t>
+          <t>operational_controls</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Subcontractor &amp; vendor risk transfer</t>
+          <t>Snow &amp; ice, security, and site vendors</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -2098,15 +2126,15 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>For subcontractors and vendors, how consistently are indemnity terms, additional-insured status, and waivers of subrogation obtained and enforced?</t>
+          <t>For snow and ice removal, security patrols, and other on-site vendors, how consistently are procedures documented and risk transferred (logs, cameras, indemnity, additional-insured status)?</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>2</v>
@@ -2120,7 +2148,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>br_data_security</t>
+          <t>br_residential_programs</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2130,25 +2158,25 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Sensitive data handling</t>
+          <t>Leasing, renters insurance &amp; fair housing</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>storesSensitiveData</t>
+          <t>hasResidentialTenants</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>For the sensitive customer, employee, or payment data you hold, how are access, vendor security, and incident response managed?</t>
+          <t>For residential tenants, how are leasing and screening, renters-insurance verification, anti-discrimination training, and short-term-rental monitoring handled?</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>2</v>
@@ -2182,12 +2210,12 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>With a workforce of this size, how are workers' compensation return-to-work, employment practices (handbook, training, documentation), and benefits data protection handled?</t>
+          <t>With on-site and corporate staff of this size, how are workers' compensation return-to-work, employment practices (handbook, training, documentation), and manager training handled?</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>3</v>
@@ -2214,7 +2242,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Board &amp; investor governance</t>
+          <t>Investors, funds &amp; lenders</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -2224,12 +2252,12 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>With outside investors or a board, how are directors &amp; officers, fiduciary, and governance-related exposures reviewed?</t>
+          <t>With outside investors, funds, or lenders, how are investor reporting, fund and entity E&amp;O and D&amp;O exposures, and lender insurance requirements managed?</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I25" s="4" t="n">
         <v>2</v>
@@ -2246,7 +2274,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>br_regulated_materials</t>
+          <t>br_environmental</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2256,22 +2284,22 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Regulated materials &amp; environmental</t>
+          <t>Environmental risks</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>regulatedMaterials</t>
+          <t>environmentalExposures</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>For regulated materials or processes, how are environmental permits, storage practices, and pollution exposure managed?</t>
+          <t>What are your practices for environmental risks at the properties (lead, mold, asbestos, oil tanks, legionella, soil contamination), including due diligence on acquisitions?</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>3</v>
@@ -2344,7 +2372,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>About 60 days out, but it varies year to year</t>
+          <t>About 60 days out; we ask brokers to market and follow up 30 days out</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2387,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>90+ days out with a written timeline</t>
+          <t>90+ days out with a written timeline and an updated statement of values</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2402,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>120+ days out with a documented calendar, owners, and a pre-renewal strategy meeting</t>
+          <t>120+ days out with a documented calendar, owners, a pre-renewal strategy meeting, and a reconciled statement of values</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2417,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>No single owner; whoever the broker contacts handles it</t>
+          <t>No single owner; whoever the broker contacts handles it, or the property manager decides</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2447,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>A named owner with defined responsibilities</t>
+          <t>A named owner with defined responsibilities, including certificates and mid-term changes</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2462,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>A named owner, a backup, and a cross-functional review (finance, operations, HR/safety)</t>
+          <t>A named owner, a backup, and a defined split of duties with the property manager, asset management, and finance</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2477,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>We renew the same limits without discussion</t>
+          <t>We trust the agent or go with past numbers; limits follow the premium budget</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2492,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>The broker recommends and we generally accept</t>
+          <t>We have discussed limits with the agent but never worked through examples or lender requirements in detail</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2507,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>We review limits against contracts, assets, and revenue annually</t>
+          <t>We review limits annually against lender and lease requirements, asset values, and revenue</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2522,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>We document the rationale for each limit and deductible and revisit it when the business changes</t>
+          <t>A formal annual process considers industry trends, risk tolerance, balance sheet, defensibility, lender covenants, and documents the rationale for each limit and deductible</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2537,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>We use last year's numbers unless someone flags a change</t>
+          <t>We don't analyze replacement cost; the insurer dictates it and values are carried forward</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2552,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>We update the big items but rarely reconcile schedules</t>
+          <t>We reviewed values a few years ago but do not update often and are not confident in the process</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2567,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Finance validates values annually against records</t>
+          <t>Values and building details are updated annually and checked against recent construction costs</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2582,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Values are reconciled against financials, fixed-asset registers, and schedules, with sign-off before submission</t>
+          <t>Values are updated annually, reconciled against rebuilds, appraisals, and recent claims, with construction, protection, and update history documented per building</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2612,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>We mention major changes when we remember</t>
+          <t>We mention major acquisitions or sales when we remember</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2627,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>A defined process captures changes and shares them with the broker</t>
+          <t>A defined process reports each acquisition, disposition, and major renovation to the broker with values and lender requirements</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2642,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Changes are logged, reviewed quarterly for insurance impact, and reflected in mid-term endorsements when needed</t>
+          <t>Changes are logged, reviewed quarterly for insurance impact, and reflected in schedules and endorsements when they happen</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2657,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>None; we sign applications and the broker handles the rest</t>
+          <t>I don't know; we have never seen what brokers present to market</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2672,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>We submit updated information annually but have not seen how our story is told to carriers</t>
+          <t>We submit updated information annually and confirm the broker understands changes to the portfolio</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2687,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>We review the submission and know which carriers quoted or declined</t>
+          <t>We review the submission and know which carriers quoted or declined and why</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2702,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>We collaborate with our broker on how best to portray the company in the marketplace, review the full submission, and receive a market summary with reasons for declinations</t>
+          <t>We collaborate with our broker to determine how best to portray the portfolio, review the full submission and narrative, and receive a market summary with reasons for declinations</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2717,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Basic antivirus; MFA and tested backups are not consistently in place</t>
+          <t>No data security program or process; information is stored locally and not encrypted</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2732,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>MFA on email; backups exist but are not tested regularly</t>
+          <t>Some form of data security, such as limited access, encryption, or occasional employee education</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2747,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>MFA on email and remote access, tested offline backups, endpoint detection, and a written incident plan</t>
+          <t>A formal data security program: MFA, encryption, limited access, regular training, and a written incident plan</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2762,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>All of the prior plus annual testing, vendor security review, and executive reporting</t>
+          <t>Formal program plus vendor security review of property-management and payment platforms, tested backups, and annual review with the broker</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2777,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>No formal protocol; an email or phone request is usually sufficient</t>
+          <t>No formal protocols; an email or phone request is usually sufficient</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2807,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Written procedure with callback verification to a known number and dual approval for all bank changes and wires</t>
+          <t>Written procedures with callback verification to a known number and dual approval for wires and bank-detail changes</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2822,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Formal written program with regular training: dual authorization, callback verification, destination confirmation, and receipt confirmation</t>
+          <t>Formal written program with regular training: dual authorization, calls to verify, destination-detail confirmation, receipt confirmation, and periodic consultation with the bank on best practices</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2837,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Training happens on the job; little is written down</t>
+          <t>Inspections happen when something breaks; little is written down</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2852,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Some written procedures; training records are incomplete</t>
+          <t>Some written procedures; inspection and maintenance records are incomplete or live only with the manager</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2867,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Written safety program, documented training, and periodic inspections</t>
+          <t>Written inspection schedule, life-safety testing records, and a preventive maintenance plan per property</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2882,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Written program with documented training, inspections, near-miss reporting, and management review of results</t>
+          <t>Written program with documented inspections, life-safety testing, lighting and security logs, preventive maintenance plans, and ownership review of results</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2897,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>It is reported when someone thinks of it, sometimes weeks later</t>
+          <t>No policies or protocols; the property manager reports claims directly to the carrier when they think of it</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2912,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Supervisors know to report, but timing and format vary</t>
+          <t>Supervisors and managers know to report, but timing and format vary; we check in with the broker when we need an update</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2927,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>A written protocol defines who reports, how, and within what timeframe</t>
+          <t>A written protocol defines who reports, how, and within what timeframe, with an incident form for every event</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2942,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Written protocol, reporting within 24–48 hours, an incident form, and tracking of every report</t>
+          <t>Written protocol, reporting within 24–48 hours, incident forms, and formal meetings with broker and adjusters on a predetermined timeline</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2957,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>We do not review open claims</t>
+          <t>We work directly with the carrier and adjuster; we do not focus on the liability claims process or communicate with assigned counsel</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2972,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Only when the carrier or broker raises something</t>
+          <t>We engage the broker if we are not satisfied; the broker primarily deals with counsel while we monitor open claims</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2987,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Scheduled reviews at least twice a year</t>
+          <t>Scheduled claim reviews at least twice a year with reserve discussion; we consider a public adjuster case by case</t>
         </is>
       </c>
     </row>
@@ -2974,7 +3002,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Quarterly claim reviews with reserve challenges, adjuster accountability, and pre-renewal loss-run reconciliation</t>
+          <t>A systematic process: quarterly reviews with reserve challenges, pre-assigned preferred defense counsel where possible, public-adjuster decisions made with the broker against policy wording, and pre-renewal loss-run reconciliation</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3032,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Supervisors discuss causes; actions are not tracked</t>
+          <t>The property manager discusses causes; actions are not tracked</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3047,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Root-cause review for significant incidents with documented corrective actions</t>
+          <t>Root-cause review for significant incidents with documented corrective actions and work orders</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3062,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Every incident gets a root-cause review, corrective actions are tracked to closure, and trends are reported to leadership</t>
+          <t>Every incident gets a root-cause review, corrective actions are tracked to closure across the portfolio, and trends are reported to ownership</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3077,7 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Often work starts on a handshake or PO alone</t>
+          <t>We don't always get contracts signed; work often starts on a proposal or a call</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3092,7 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Contracts exist for major relationships; smaller ones vary</t>
+          <t>An attorney reviews or writes contracts and we make sure they are signed</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3107,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Signed contracts are required before work begins</t>
+          <t>Attorney-reviewed contracts plus broker review for insurance and risk-transfer terms; signed before work starts</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3122,7 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Signed contracts required, with standard indemnity and insurance language reviewed by counsel and tracked centrally</t>
+          <t>Attorney and broker review, signed before work starts, master agreements with key vendors, and payment blocked when contract or insurance terms are missing</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3137,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>We do not set requirements; we accept whatever the other party proposes</t>
+          <t>We do not set requirements; we accept whatever the tenant, vendor, or lender proposes</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3152,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>We use a generic requirement list without reviewing it</t>
+          <t>We use generic lease and contract language without reviewing it</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3167,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Requirements are defined by relationship type and reviewed by broker or counsel</t>
+          <t>Requirements are defined by relationship type (tenant, vendor, contractor) and reviewed by broker or counsel</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3182,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Requirements are defined, reviewed annually, and cross-checked against our own policies and customer demands</t>
+          <t>Requirements are defined, reviewed annually, cross-checked against our own policies and every lender and management-agreement obligation, and enforced</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3197,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>We collect certificates when asked but do not review them</t>
+          <t>We don't; certificates are collected when asked and not reviewed</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3212,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Someone checks that a certificate exists; endorsements are rarely verified</t>
+          <t>We obtain certificates with additional-insured status and check coverage and limit adequacy, but tracking is manual and infrequent</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3227,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Certificates and required endorsements are verified before work and on expiration</t>
+          <t>Certificates and required endorsements are verified before work and on expiration, in a tracking system</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3242,7 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Verification is tracked in a system, endorsements are matched to contract terms, and non-compliance is escalated</t>
+          <t>Software tracks every vendor's insurance in real time, the broker reviews complete policies for key contractors, endorsements are matched to contract terms, and non-compliant vendors are stopped from working</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3272,7 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>More than 18 months ago, or only when a new broker or agent first came on board</t>
+          <t>More than 18 months ago, or only when a new agent first came on board</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3287,7 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>An annual risk review with a documented risk list</t>
+          <t>Annually, with a documented list of risks by property</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3302,7 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Annual review with owners, action plans, and quarterly progress updates to leadership</t>
+          <t>Annually with owners and action plans, reviewed with the broker so prevention, mitigation, and insurance stay aligned</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3317,7 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>We learn about changes when we are notified of a violation or audit</t>
+          <t>We learn about changes when we are notified of a violation, complaint, or audit</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3347,7 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>A defined owner monitors regulations and briefs leadership</t>
+          <t>A defined owner monitors regulations, and required training and postings are documented</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3362,7 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Defined owner, documented compliance calendar, and periodic compliance audits</t>
+          <t>Defined owner, documented compliance calendar, annual training with records, and periodic compliance audits with counsel</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3392,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Sometimes, for very large changes</t>
+          <t>Sometimes, for very large acquisitions</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3407,7 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>A review step is included in the launch process</t>
+          <t>A review step with the broker is part of acquisition due diligence and major operational changes</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3422,7 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Documented pre-launch review with operations, finance, broker input, and follow-up after launch</t>
+          <t>Documented pre-acquisition and pre-launch review (environmental due diligence, valuation, lender requirements, new exposures) with follow-up after closing</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3437,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Values are carried forward; building updates and carrier recommendations are not tracked</t>
+          <t>We do as little as possible; updates and flood zones are not documented</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3452,7 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Values were reviewed a few years ago; we do the minimum needed to stay compliant with carrier recommendations</t>
+          <t>We do the bare minimum to stay compliant with the insurer; updates are partially documented</t>
         </is>
       </c>
     </row>
@@ -3439,7 +3467,7 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Replacement and BI values are reviewed annually; update history and recommendation responses are documented</t>
+          <t>An active protocol responds to and tracks recommendations; roof, sprinkler, electrical, and boiler updates are documented with dates</t>
         </is>
       </c>
     </row>
@@ -3454,14 +3482,14 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Professional valuation within three years, BI worksheet, flood zone determination, documented inspections and update history, and an active protocol for responding to and tracking every carrier recommendation</t>
+          <t>Active protocol for every recommendation with completion shown to the carrier, documented update history per building, flood zone determinations, and a professional valuation within three years</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>br_fleet_controls</t>
+          <t>br_management_agreement</t>
         </is>
       </c>
       <c r="B78" s="4" t="n">
@@ -3469,14 +3497,14 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>We do not run MVRs consistently; personal vehicle use is not addressed</t>
+          <t>We do not review these requirements in agreements with our property managers</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>br_fleet_controls</t>
+          <t>br_management_agreement</t>
         </is>
       </c>
       <c r="B79" s="4" t="n">
@@ -3484,14 +3512,14 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>MVRs at hire only; no written fleet policy</t>
+          <t>We accept the terms and conditions in the manager's boilerplate agreement</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>br_fleet_controls</t>
+          <t>br_management_agreement</t>
         </is>
       </c>
       <c r="B80" s="4" t="n">
@@ -3499,14 +3527,14 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Written fleet policy, annual MVRs, and a defined hired/non-owned auto approach</t>
+          <t>Counsel reviewed the agreement; we know who insures what and hold the manager's certificate</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>br_fleet_controls</t>
+          <t>br_management_agreement</t>
         </is>
       </c>
       <c r="B81" s="4" t="n">
@@ -3514,14 +3542,14 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Written policy, annual MVRs with disqualification criteria, telematics or cameras, and driver training records</t>
+          <t>We actively review and dictate the insurance and indemnity terms, require adequate limits and coverages from the manager, and regularly request updated certificates to confirm they are in place</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>br_subcontractor_transfer</t>
+          <t>br_vendor_transfer</t>
         </is>
       </c>
       <c r="B82" s="4" t="n">
@@ -3529,14 +3557,14 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>We rely on the vendor's own paperwork</t>
+          <t>Employees or vendors handle it informally; no logs and contracts have not been reviewed</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>br_subcontractor_transfer</t>
+          <t>br_vendor_transfer</t>
         </is>
       </c>
       <c r="B83" s="4" t="n">
@@ -3544,14 +3572,14 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Our agreement includes the terms, but we rarely confirm the endorsements</t>
+          <t>Employees are trained or contractors are hired, but snow logs, security procedures, and contract terms are inconsistent</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>br_subcontractor_transfer</t>
+          <t>br_vendor_transfer</t>
         </is>
       </c>
       <c r="B84" s="4" t="n">
@@ -3559,14 +3587,14 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Terms are standard and endorsements are confirmed before work</t>
+          <t>Every snow removal and patrol is documented, and vendors indemnify and name us as additional insured</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>br_subcontractor_transfer</t>
+          <t>br_vendor_transfer</t>
         </is>
       </c>
       <c r="B85" s="4" t="n">
@@ -3574,14 +3602,14 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Terms are standard, endorsements confirmed, non-compliant vendors are stopped from working, and exceptions are approved in writing</t>
+          <t>Documented logs visible on cameras, written security and snow procedures, contracts reviewed for indemnity and additional-insured terms, and vendor insurance tracked in a compliance system</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>br_data_security</t>
+          <t>br_residential_programs</t>
         </is>
       </c>
       <c r="B86" s="4" t="n">
@@ -3589,14 +3617,14 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Access is broad; we have not reviewed vendor security or an incident plan</t>
+          <t>No formal process; renters insurance is not tracked and fair-housing training is informal</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>br_data_security</t>
+          <t>br_residential_programs</t>
         </is>
       </c>
       <c r="B87" s="4" t="n">
@@ -3604,14 +3632,14 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Access is limited informally; incident response is undocumented</t>
+          <t>Application with employment verification and some screening; renters insurance tracked manually and updated infrequently; handbook statement only</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>br_data_security</t>
+          <t>br_residential_programs</t>
         </is>
       </c>
       <c r="B88" s="4" t="n">
@@ -3619,14 +3647,14 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Role-based access, vendor security review, and a written incident response plan</t>
+          <t>Attorney-vetted application and lease, background checks, renters insurance required and tracked, annual fair-housing training, lease prohibits short-term rentals</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>br_data_security</t>
+          <t>br_residential_programs</t>
         </is>
       </c>
       <c r="B89" s="4" t="n">
@@ -3634,7 +3662,7 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>All of the prior plus annual tabletop exercises, data inventory, and breach-notification readiness</t>
+          <t>All of the prior plus software that monitors renters insurance in real time and force-places when missing, documented annual training with counsel consultation, and active monitoring for short-term rental use</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3722,7 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>All of the prior plus experience-mod review, claims-trend analysis, and annual employment-practices training</t>
+          <t>All of the prior plus experience-mod review, claims-trend analysis, and annual employment-practices training with records</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3737,7 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>They have not been reviewed</t>
+          <t>Updates are provided on demand; entity coverages and lender requirements have not been reviewed</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3752,7 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Coverage was placed at the time of investment and not revisited</t>
+          <t>Annual performance updates; coverage was placed at the time of the raise and not revisited</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3767,7 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Reviewed annually with the broker against bylaws, investor agreements, and benefit plans</t>
+          <t>Quarterly reporting on performance and key metrics; E&amp;O and D&amp;O reviewed annually with the broker against fund documents; lender requirements tracked</t>
         </is>
       </c>
     </row>
@@ -3754,14 +3782,14 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Annual review plus board reporting on limits, indemnification agreements, and fiduciary controls</t>
+          <t>Quarterly reporting with online access, annual review of entity coverages, every legal entity confirmed as a named insured, and lender requirements reconciled at each closing</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>br_regulated_materials</t>
+          <t>br_environmental</t>
         </is>
       </c>
       <c r="B98" s="4" t="n">
@@ -3769,14 +3797,14 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>We are not sure what permits apply; storage practices are informal</t>
+          <t>I don't know; we have not looked at it</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>br_regulated_materials</t>
+          <t>br_environmental</t>
         </is>
       </c>
       <c r="B99" s="4" t="n">
@@ -3784,14 +3812,14 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Permits are in place; documentation of storage and disposal is inconsistent</t>
+          <t>We depend on what we read and hear from industry groups; we may purchase environmental insurance</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>br_regulated_materials</t>
+          <t>br_environmental</t>
         </is>
       </c>
       <c r="B100" s="4" t="n">
@@ -3799,14 +3827,14 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Permits, storage, and disposal are documented with a compliance owner</t>
+          <t>An environmental specialist has reviewed the portfolio and surveys; environmental due diligence is part of acquisitions</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>br_regulated_materials</t>
+          <t>br_environmental</t>
         </is>
       </c>
       <c r="B101" s="4" t="n">
@@ -3814,7 +3842,7 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Documented compliance program, periodic environmental audits, and pollution exposure reviewed with the broker</t>
+          <t>Specialist reviews the portfolio routinely, moisture and mold procedures are written, lender environmental conditions are tracked, and environmental insurance is reviewed with the broker</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3868,31 +3896,35 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>logistics_3pl</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr"/>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>For a 3PL this includes the value of customers' goods in your care, custody, and control, vehicle and trailer schedules, and square footage by location.</t>
+          <t>Include unit counts, rent roll and business-income values, and any building improvements since the last valuation.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>mkt_exposure_data</t>
+          <t>ops_safety_training</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>light_manufacturing</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr"/>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>How are unit and common-area inspections, life-safety systems (smoke and CO detectors, sprinklers, egress), lighting, and preventive maintenance documented across the communities?</t>
+        </is>
+      </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>For a manufacturer this includes machinery and equipment values, a business-interruption worksheet, and any dependence on a single supplier or customer.</t>
+          <t>Habitability claims turn on documentation: inspection logs, work-order completion, and life-safety testing records.</t>
         </is>
       </c>
     </row>
@@ -3904,157 +3936,73 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>logistics_3pl</t>
+          <t>cre_owner</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>How are warehouse and dock safety (forklift certification, racking, housekeeping), fire protection (sprinkler inspections, impairment procedures, commodity storage), and driver training documented?</t>
+          <t>How are roof, sprinkler, electrical, and boiler inspections, life-safety systems, and preventive maintenance documented across the buildings?</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Warehouse underwriters look first at fire protection and forklift and dock injury controls.</t>
+          <t>Roof age, sprinkler impairments, aluminum wiring, and boiler condition are the recommendations carriers issue most often.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>ops_safety_training</t>
+          <t>crt_insurance_requirements</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>light_manufacturing</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>How are machine guarding, lockout/tagout, hearing and respiratory protection, and safety training documented?</t>
-        </is>
-      </c>
+          <t>cre_owner</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Machine guarding and lockout/tagout drive both workers' compensation experience and product-safety credibility with underwriters.</t>
+          <t>Commercial leases typically require tenant liability and property coverage with the owner as additional insured; lenders require specific limits, mortgagee clauses, and flood where applicable.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>crt_signed_contracts</t>
+          <t>crt_insurance_requirements</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>logistics_3pl</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Before goods are received or work begins, how consistently are written warehousing agreements, customer contracts, and carrier/vendor agreements in place?</t>
-        </is>
-      </c>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Warehouse receipts and customer contracts define your legal liability for goods in your care. Unsigned or inconsistent terms are a common gap.</t>
+          <t>Vendor requirements matter most here: snow and ice, security, and renovation contractors should indemnify and name the owner and manager as additional insureds.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>crt_signed_contracts</t>
+          <t>emr_regulatory</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>light_manufacturing</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>How consistently are written supply agreements, customer purchase terms, and vendor contracts in place before production or shipment begins?</t>
-        </is>
-      </c>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Customer terms often carry product warranty, recall, and indemnity obligations that shape your liability program.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>crt_insurance_requirements</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>logistics_3pl</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Customers commonly require warehouse legal liability, cargo, and auto limits. Carriers and subcontracted haulers should be held to defined requirements in return.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>crt_insurance_requirements</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>light_manufacturing</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Large customers often specify product liability limits and vendor endorsements; suppliers should be held to defined requirements for the components they provide.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>emr_new_activity_review</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>logistics_3pl</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>When you take on a new commodity, temperature-controlled or hazardous storage, a new customer contract, or a new facility, is risk and insurance impact reviewed beforehand?</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>emr_new_activity_review</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>light_manufacturing</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>When you launch a new product, add a production line or process, or enter a new market, is product liability, recall, and business-interruption impact reviewed beforehand?</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr"/>
+          <t>Fair-housing training records, required postings, and consistent screening criteria are the first things asked about in a discrimination claim.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4067,7 +4015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4132,17 +4080,17 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Your renewal process may begin too late to fully document your risk controls.</t>
+          <t>Your renewal process may begin too late to fully document the portfolio.</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Renewal preparation appears to begin with limited runway. Controls that are not documented in time rarely make it into the submission carriers evaluate.</t>
+          <t>Renewal preparation appears to begin with limited runway. Updated values, building improvements, and closed carrier recommendations that are not documented in time rarely make it into the submission carriers evaluate.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Benchmark indication: high-impact underwriting strengths were identified elsewhere in your answers, but they may not be incorporated consistently into carrier submissions.</t>
+          <t>Benchmark indication: strengths were identified elsewhere in your answers, but they may not be incorporated consistently into what carriers see.</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -4167,17 +4115,17 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Your contracts and insurance-verification process may not be operating as one control system.</t>
+          <t>Your leases, vendor contracts, and certificate tracking may not be operating as one control system.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Answers about signed contracts, insurance requirements, and certificate verification are uneven. Risk transfer only works when all three align.</t>
+          <t>Answers about signed vendor contracts, insurance requirements, and certificate verification are uneven. Risk transfer only works when the requirement, the contract, and the certificate line up.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Potential opportunity: review whether contractual requirements, certificates of insurance, and policy endorsements align for your largest customer and vendor relationships.</t>
+          <t>Potential opportunity: review whether lease and contract requirements, certificates of insurance, and endorsements align for your largest tenants and your snow, security, and renovation vendors.</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -4202,17 +4150,17 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Your business has changed faster than your insurance-governance process.</t>
+          <t>Your portfolio has changed faster than your insurance-governance process.</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>You reported recent acquisitions or new locations, but operational changes reach the insurance program late or inconsistently.</t>
+          <t>You reported recent acquisitions, dispositions, or major renovations, but portfolio changes reach the insurance program late or inconsistently.</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Areas to investigate: new locations, increased payroll, new services, and updated property values, and whether each is reflected in current schedules.</t>
+          <t>Areas to investigate: newly acquired properties, updated replacement values, lender requirements at each closing, and whether renovations are reflected in schedules.</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -4242,12 +4190,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Incident reporting, open-claim review, or corrective-action tracking appear informal. Claims that are not managed tend to cost more and stay open longer.</t>
+          <t>Incident reporting, open-claim review, or corrective-action tracking appear informal, and there is no systematic broker process for advocacy, counsel, or public adjusters.</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Potential opportunity: evaluate reporting timelines, reserve review, adjuster accountability, and how corrective actions are tracked to closure.</t>
+          <t>Potential opportunity: evaluate reporting timelines, reserve review, carrier-assigned counsel, public-adjuster decisions, and how corrective actions are tracked across properties.</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -4272,17 +4220,17 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Incomplete exposure data or a weak underwriting narrative could limit your market options.</t>
+          <t>A statement of values that carriers do not trust, or a story they never hear, could limit your market options.</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Exposure values appear to be carried forward without reconciliation, or you have limited visibility into what carriers receive.</t>
+          <t>Replacement costs appear to be dictated by the insurer or carried forward, or you have limited visibility into what carriers receive about the portfolio.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Pricing cannot be assessed from this questionnaire alone. However, carriers generally offer their best terms to accounts that present validated data and a clear narrative, subject to policy, loss, and underwriting review.</t>
+          <t>Pricing cannot be assessed from this questionnaire alone. However, carriers generally offer their best terms to portfolios that present validated values, documented building updates, and a clear narrative, subject to policy, loss, and underwriting review.</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -4307,17 +4255,17 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Payment-change and wire controls may leave a path open for social-engineering losses.</t>
+          <t>Funds-transfer controls may leave a path open for social-engineering losses.</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Vendor bank-detail changes or wires may be released without callback verification and dual approval. This is the most common route for funds-transfer fraud.</t>
+          <t>Wires, vendor bank-detail changes, or security-deposit returns may be released without callback verification and dual approval. This is the most common route for funds-transfer fraud in property operations.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Potential opportunity: confirm callback procedures, approval thresholds, and whether crime or cyber coverage includes social-engineering terms, subject to policy review.</t>
+          <t>Potential opportunity: confirm callback procedures, approval thresholds, controls at the property-management company, and whether crime or cyber coverage includes social-engineering terms, subject to policy review.</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -4342,22 +4290,22 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Cyber controls may not meet the minimums that most carriers now require.</t>
+          <t>Protection of tenant, applicant, and investor data may not meet the minimums cyber carriers now require.</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Multi-factor authentication, tested backups, and a written incident plan are the controls cyber underwriters ask about first.</t>
+          <t>Multi-factor authentication, encryption, tested backups, and a written incident plan are the controls cyber underwriters ask about first, along with the security of your property-management platform.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Potential opportunity: document current controls, close gaps before the next cyber application, and confirm which controls are attested on existing applications.</t>
+          <t>Potential opportunity: document current controls, review the property-management and payment vendors' security, and confirm which controls are attested on existing applications.</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>ops_cyber_controls, br_data_security</t>
+          <t>ops_cyber_controls</t>
         </is>
       </c>
     </row>
@@ -4377,17 +4325,17 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Insurance program ownership appears informal.</t>
+          <t>Insurance program ownership appears informal or split with the property manager.</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Without a named owner and defined responsibilities, renewal tasks, certificate requests, and mid-term changes tend to fall through the cracks.</t>
+          <t>Without a named owner and a defined split of duties, certificate requests, mid-term acquisitions, and lender requirements tend to fall through the cracks.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Potential opportunity: assign an owner and backup, and define the touchpoints with finance, operations, and HR/safety.</t>
+          <t>Potential opportunity: assign an owner and backup, and define who handles certificates, closings, and claims between ownership and the manager.</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -4412,17 +4360,17 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Limits and deductibles appear to be renewed without a documented rationale.</t>
+          <t>Limits and deductibles appear to follow the budget rather than a documented rationale.</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>This diagnostic does not assess whether limits are adequate. It does note that limits which are never revisited may not track contract requirements or asset growth.</t>
+          <t>This diagnostic does not assess whether limits are adequate. It does note that limits which are never revisited may not track lender covenants, lease requirements, or portfolio growth.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Potential opportunity: document the basis for each limit and deductible with a licensed advisor and revisit it when contracts or assets change.</t>
+          <t>Potential opportunity: document the basis for each limit and deductible with a licensed advisor, including key liability cases and lender requirements, and revisit it as the portfolio changes.</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -4447,17 +4395,17 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Safety and training practices may exist but are not documented in a form underwriters can credit.</t>
+          <t>Inspection, life-safety, and maintenance practices may exist but are not documented in a form underwriters can credit.</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Written programs, training records, and inspection logs are what carriers use to distinguish a well-run operation from an average one.</t>
+          <t>Inspection schedules, life-safety testing records, lighting logs, and preventive maintenance plans are what carriers use to distinguish a well-run portfolio from an average one.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Potential opportunity: assemble a safety documentation package before the next submission.</t>
+          <t>Potential opportunity: assemble an inspection and maintenance documentation package per property before the next submission.</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -4478,21 +4426,21 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Owned-property values and building updates may be undocumented.</t>
+          <t>Carrier recommendations and building updates may not be tracked or shown to the market.</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Replacement cost, business-interruption values, flood exposure, and building-system updates drive both coverage terms and pricing conversations.</t>
+          <t>How you respond to sprinkler, wiring, boiler, and roof recommendations, and whether updates and flood exposure are documented, drives both coverage terms and pricing conversations.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Areas to investigate: date of last valuation, BI worksheet, flood zone determination, and documented roof, sprinkler, and electrical updates.</t>
+          <t>Areas to investigate: open recommendations by property, completion evidence, roof and system update dates, flood zone determinations, and the date of the last professional valuation.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -4504,47 +4452,47 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>fleet_controls</t>
+          <t>management_agreement_gap</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>operational_controls</t>
+          <t>contractual_risk_transfer</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Fleet and driver controls may not be documented to the level auto underwriters expect.</t>
+          <t>The insurance and indemnity terms in your property-management agreement may not have been reviewed.</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>MVR practices, fleet policy, and hired/non-owned auto handling are primary controls for commercial auto.</t>
+          <t>Boilerplate management agreements often leave it unclear who insures what and who indemnifies whom when a loss occurs at a managed property.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Potential opportunity: adopt a written fleet policy with annual MVRs and disqualification criteria.</t>
+          <t>Potential opportunity: have counsel and the broker review the agreement, dictate required limits and coverages, and hold current certificates from the manager.</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>br_fleet_controls</t>
+          <t>br_management_agreement</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>subcontractor_transfer_gap</t>
+          <t>site_vendor_gap</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>contractual_risk_transfer</t>
+          <t>operational_controls</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -4552,29 +4500,29 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Subcontractor and vendor risk transfer may not be enforced.</t>
+          <t>Snow and ice, security, and site-vendor procedures may not be documented or transferring risk.</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Indemnity terms and endorsements that are not confirmed before work begins may not respond when a loss occurs.</t>
+          <t>Slip-and-fall and premises claims turn on logs, cameras, and whether the vendor's contract indemnifies and insures you.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Potential opportunity: confirm additional-insured and waiver endorsements for active vendors.</t>
+          <t>Potential opportunity: require documented snow logs and patrol procedures, and confirm indemnity and additional-insured terms for every site vendor.</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>br_subcontractor_transfer</t>
+          <t>br_vendor_transfer</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>workforce_programs_gap</t>
+          <t>residential_programs_gap</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -4583,129 +4531,164 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Workforce programs (return-to-work, handbook, manager training) may be informal for a company of your size.</t>
+          <t>Leasing, renters-insurance, and fair-housing practices may be informal for the size of the residential portfolio.</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>These programs influence workers' compensation experience and employment-practices exposure.</t>
+          <t>Renters insurance that is not tracked, screening that is not consistent, and training that is not documented all show up in liability and discrimination claims.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Potential opportunity: document return-to-work procedures and update the employee handbook.</t>
+          <t>Potential opportunity: evaluate real-time renters-insurance monitoring, attorney-vetted lease and screening criteria, and documented annual fair-housing training.</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>br_workforce_programs</t>
+          <t>br_residential_programs</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>investor_governance_gap</t>
+          <t>workforce_programs_gap</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>operational_controls</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Board and investor-related exposures may not have been reviewed since the investment.</t>
+          <t>Workforce programs (return-to-work, handbook, manager training) may be informal for a staff of your size.</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Directors &amp; officers, fiduciary, and indemnification arrangements are typically revisited as ownership and boards change.</t>
+          <t>These programs influence workers' compensation experience and employment-practices exposure across on-site teams.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Potential opportunity: review governance-related exposures with a licensed advisor against current bylaws and investor agreements.</t>
+          <t>Potential opportunity: document return-to-work procedures and update the employee handbook.</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>br_governance_investors</t>
+          <t>br_workforce_programs</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>environmental_gap</t>
+          <t>investor_governance_gap</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>emerging_risk</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Environmental compliance and pollution exposure may not be documented.</t>
+          <t>Investor, fund, and lender-related exposures may not have been reviewed since the last capital event.</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Permits, storage practices, and disposal records are the starting point for any environmental conversation with carriers.</t>
+          <t>Fund and entity E&amp;O and D&amp;O, named-insured completeness across every LLC, and lender requirements are typically revisited as deals close and boards change.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Areas to investigate: applicable permits, storage documentation, and whether pollution exposure has been reviewed.</t>
+          <t>Potential opportunity: review entity coverages with a licensed advisor against fund documents and confirm every legal entity is scheduled as a named insured.</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>br_regulated_materials</t>
+          <t>br_governance_investors</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>environmental_gap</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>emerging_risk</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Environmental exposures at the properties may not have been reviewed.</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Lead, mold, asbestos, oil tanks, legionella, and soil conditions are the starting point for any environmental conversation with carriers and lenders.</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Areas to investigate: environmental surveys on file, acquisition due diligence, moisture and mold procedures, lender environmental conditions, and whether pollution exposure has been reviewed.</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>br_environmental</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>emerging_risk_unmanaged</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>emerging_risk</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C19" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>New activities and regulatory changes may reach the insurance program after the fact.</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Without a pre-launch review step, new locations, products, and technology can create exposures that are not reflected until the next renewal.</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Potential opportunity: add a risk and insurance checkpoint to your launch process.</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Acquisitions, regulatory changes, and new exposures may reach the insurance program after the fact.</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Without a pre-acquisition and pre-launch review step, new properties, short-term rentals, EV charging, and lithium-battery storage can create exposures that are not reflected until the next renewal.</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Potential opportunity: add a risk and insurance checkpoint to acquisition due diligence and to operational changes at the properties.</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>emr_new_activity_review, emr_regulatory, emr_annual_review</t>
         </is>
@@ -4790,7 +4773,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>How ready is your company to be evaluated by the insurance market?</t>
+          <t>How ready is your real estate portfolio to be evaluated by the insurance market?</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -4800,7 +4783,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>CFOs, COOs, and owners unsure whether the company is presenting an accurate, differentiated risk story.</t>
+          <t>Owners, asset managers, and CFOs unsure whether the portfolio is presenting an accurate, differentiated risk story.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr"/>
@@ -4820,17 +4803,17 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Is your next renewal on a timeline, or on autopilot?</t>
+          <t>Is your property renewal on a timeline, or on autopilot?</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>A confidential check of your renewal runway, the data carriers will ask for, and the changes that need to be documented before submissions go out.</t>
+          <t>A confidential check of your renewal runway, the statement of values carriers will scrutinize, and the acquisitions and updates that need to be documented before submissions go out.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>CFOs and risk managers facing a renewal within three to nine months.</t>
+          <t>Owners, asset managers, and CFOs facing a property renewal within three to nine months.</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -4845,7 +4828,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Timing, data, and the story carriers receive. These answers determine whether preparation starts early enough to matter.</t>
+          <t>Timing, values, and the story carriers receive. These answers determine whether preparation starts early enough to matter.</t>
         </is>
       </c>
     </row>
@@ -4862,17 +4845,17 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Are your contracts actually transferring risk, or just describing it?</t>
+          <t>Are your leases and vendor contracts actually transferring risk, or just describing it?</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>A confidential scan of how signed contracts, insurance requirements, certificates, and subcontractor terms work together as one control system.</t>
+          <t>A confidential scan of how leases, vendor and snow-removal contracts, management agreements, insurance requirements, and certificate tracking work together as one control system.</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>COOs and CFOs in construction, manufacturing, real estate, and logistics who rely on vendors and subcontractors.</t>
+          <t>Owners and property managers who rely on tenants' insurance and on-site vendors.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -4882,12 +4865,12 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Your contract-risk workflow</t>
+          <t>Your lease and vendor risk-transfer workflow</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Requirements that are never verified, and certificates that are never matched to contracts, do not transfer risk when a loss occurs.</t>
+          <t>Requirements that are never verified, and certificates that are never matched to leases and contracts, do not transfer risk when a loss occurs.</t>
         </is>
       </c>
     </row>
@@ -4904,17 +4887,17 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Are claims being managed, or just reported?</t>
+          <t>Are claims at your properties being managed, or just reported?</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>A confidential look at reporting speed, open-claim cadence, return-to-work practices, and how corrective actions are tracked.</t>
+          <t>A confidential look at reporting speed, open-claim cadence, public-adjuster and counsel practices, and how corrective actions are tracked across the portfolio.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>CFO, HR, and operations leaders frustrated by recurring or poorly managed claims.</t>
+          <t>Owners, asset managers, and property managers frustrated by recurring or poorly managed claims.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -4929,7 +4912,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Late reporting, unreviewed reserves, and untracked corrective actions are the most common reasons claims cost more and stay open longer.</t>
+          <t>Late reporting, unreviewed reserves, unmanaged counsel, and untracked corrective actions are the most common reasons property claims cost more and stay open longer.</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4990,27 +4973,27 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>logistics_3pl</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>3PL / warehousing / distribution</t>
+          <t>Multifamily / apartment communities</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>logistics_3pl</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Fleet, property, cargo, labor, contracts</t>
+          <t>Tenant, premises, discrimination</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Cargo, auto, warehouse legal liability, fire protection</t>
+          <t>Renters insurance, habitability, EPLI, vendor controls</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -5022,59 +5005,59 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>food_cold_storage</t>
+          <t>office</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Food distribution / cold storage</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>logistics_3pl</t>
+          <t>cre_owner</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Spoilage and temperature dependency</t>
+          <t>Property values and tenant improvements</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Refrigeration breakdown, recall, contamination</t>
+          <t>SOV quality, lease requirements, BI, life safety</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>light_manufacturing</t>
+          <t>industrial_flex</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Light / advanced manufacturing</t>
+          <t>Industrial / flex / warehouse</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>light_manufacturing</t>
+          <t>cre_owner</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Property, machinery, products, WC</t>
+          <t>Large replacement values and tenant operations</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Business interruption, machine guarding, product liability</t>
+          <t>SOV quality, sprinkler and roof condition, tenant contracts, environmental</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -5086,76 +5069,76 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>life_sciences</t>
+          <t>retail_mixed_use</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Life-sciences supplier</t>
+          <t>Retail / mixed-use</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>light_manufacturing</t>
+          <t>cre_owner</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>High-value inventory and regulated work</t>
+          <t>Premises liability and vendor dependence</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Clinical/product liability, cold chain, cyber, E&amp;O</t>
+          <t>Snow and ice, security, lease requirements, liquor tenants</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>contractors</t>
+          <t>net_lease</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Contractor / trades</t>
+          <t>Net-lease / single-tenant</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>cre_owner</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Subcontracting and contractual risk</t>
+          <t>Lease-driven insurance obligations</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Wrap-ups, fleet, jobsite safety, certificates</t>
+          <t>Tenant compliance tracking, lender requirements, named insureds</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>cre_owners</t>
+          <t>self_storage</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Commercial real estate owner</t>
+          <t>Self-storage</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -5165,12 +5148,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Property values and vendor dependence</t>
+          <t>Property, customer goods, access control</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>SOV quality, flood, BI, leases, management agreements</t>
+          <t>Customer goods legal liability, security, tenant insurance programs</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -5182,12 +5165,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>hospitality</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Multifamily / property manager</t>
+          <t>Hospitality / hotel assets</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -5197,12 +5180,12 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Tenant, premises, discrimination</t>
+          <t>Property, liquor, events, seasonal labor</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Renters insurance, habitability, EPLI, vendor controls</t>
+          <t>Liquor, pools, events, management agreements, D&amp;O</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -5214,12 +5197,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>healthcare</t>
+          <t>senior_housing</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Healthcare practice / MSO</t>
+          <t>Senior housing / assisted living</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -5229,12 +5212,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Professional, privacy, employment</t>
+          <t>Severe liability and workforce exposure</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Medical professional, cyber, regulatory, credentialing</t>
+          <t>Abuse controls, professional liability, staffing, auto</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -5246,44 +5229,44 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>senior_living</t>
+          <t>student_housing</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Senior living / home care</t>
+          <t>Student housing</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Severe liability and workforce exposure</t>
+          <t>Turnover, premises, parental guarantees</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Abuse controls, auto, professional liability, staffing</t>
+          <t>Renters insurance, security, event and alcohol exposure</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>professional_services</t>
+          <t>association</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Professional services</t>
+          <t>Condo / HOA association</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -5293,12 +5276,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>E&amp;O, cyber, executive risk</t>
+          <t>Governance, common areas, D&amp;O</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Contract scope, client concentration, privacy</t>
+          <t>D&amp;O, master policy allocation, vendor controls, reserves</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -5310,76 +5293,76 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>technology_msp</t>
+          <t>third_party_manager</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Technology / MSP</t>
+          <t>Third-party property manager</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Contractual and cyber aggregation</t>
+          <t>Management-agreement exposure across many owners</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Tech E&amp;O, ransomware, dependent business interruption</t>
+          <t>Management agreements, E&amp;O, tenant discrimination, funds handling</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>auto_dealers</t>
+          <t>developer</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Auto dealer / fleet business</t>
+          <t>Developer / owner-builder</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>cre_owner</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Inventory, garage, drivers</t>
+          <t>Construction and lease-up risk</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Garage liability, false pretense, cyber, weather</t>
+          <t>Builders risk, wrap-ups, contractor certificates, lender requirements</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>hospitality_clubs</t>
+          <t>land</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Hospitality / country club</t>
+          <t>Land / agricultural holdings</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -5389,12 +5372,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Property, liquor, events, seasonal labor</t>
+          <t>Premises and environmental</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Liquor, golf carts, pools, events, D&amp;O</t>
+          <t>Environmental, premises, trespass</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -5406,12 +5389,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>nonprofit</t>
+          <t>other</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Nonprofit / social services</t>
+          <t>Something else</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -5419,41 +5402,9 @@
           <t>other</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Governance, volunteers, vulnerable clients</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>D&amp;O, abuse/molestation controls, professional liability</t>
-        </is>
-      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Something else</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>no</t>
         </is>

--- a/docs/marketready-question-bank.xlsx
+++ b/docs/marketready-question-bank.xlsx
@@ -480,7 +480,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from code on 2026-09-02T21:30:54.262Z. Regenerate with: npm run docs:bank</t>
+          <t>Generated from code on 2026-09-02T21:35:51.691Z. Regenerate with: npm run docs:bank</t>
         </is>
       </c>
     </row>
